--- a/registration_forms/043_employee_appreciation_luncheon_registration--registration_forms.xlsx
+++ b/registration_forms/043_employee_appreciation_luncheon_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>message_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Message 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>start_time_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Start Time</t>
+          <t>Start Time 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1962,856 +1962,6 @@
       <c r="C60" t="inlineStr">
         <is>
           <t>11:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>12:00_am</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>12:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>12:30_am</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>12:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>01:00_am</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>01:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>01:30_am</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>01:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>02:00_am</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>02:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>02:30_am</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>02:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>03:00_am</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>03:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>03:30_am</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>03:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>04:00_am</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>04:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>04:30_am</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>04:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>05:00_am</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>05:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>05:30_am</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>05:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>06:00_am</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>06:30_am</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>06:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>07:00_am</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>07:30_am</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>07:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>08:00_am</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>08:30_am</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>09:00_am</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>09:30_am</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>09:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>10:00_am</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>10:30_am</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>10:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>11:00_am</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>11:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>11:30_am</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>11:30 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>12:00_pm</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>12:30_pm</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>12:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>01:00_pm</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>01:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>01:30_pm</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>01:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>02:00_pm</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>02:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>02:30_pm</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>02:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>03:00_pm</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>03:30_pm</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>03:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>04:00_pm</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>04:30_pm</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>05:00_pm</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>05:30_pm</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>06:00_pm</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>06:30_pm</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>07:00_pm</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>07:30_pm</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>07:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>08:00_pm</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>08:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>08:30_pm</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>08:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>09:00_pm</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>09:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>09:30_pm</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>09:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>10:00_pm</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>10:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>10:30_pm</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>10:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>11:00_pm</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>11:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>11:30_pm</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>11:30 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>12:00_am</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>12:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>start_time_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>12:30_am</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>12:30 AM</t>
         </is>
       </c>
     </row>
